--- a/Vendor RMA Guidelines.xlsx
+++ b/Vendor RMA Guidelines.xlsx
@@ -2197,7 +2197,7 @@
       </c>
       <c r="W13" s="10" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="X13" s="11" t="inlineStr">

--- a/Vendor RMA Guidelines.xlsx
+++ b/Vendor RMA Guidelines.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AJ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -562,6 +562,12 @@
     <col width="18" customWidth="1" min="28" max="28"/>
     <col width="18" customWidth="1" min="29" max="29"/>
     <col width="18" customWidth="1" min="30" max="30"/>
+    <col width="18" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -715,6 +721,36 @@
           <t>Verizon</t>
         </is>
       </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
@@ -867,6 +903,36 @@
           <t>DND</t>
         </is>
       </c>
+      <c r="AE2" s="1" t="inlineStr">
+        <is>
+          <t>A+</t>
+        </is>
+      </c>
+      <c r="AF2" s="1" t="inlineStr">
+        <is>
+          <t>A-</t>
+        </is>
+      </c>
+      <c r="AG2" s="1" t="inlineStr">
+        <is>
+          <t>B+</t>
+        </is>
+      </c>
+      <c r="AH2" s="1" t="inlineStr">
+        <is>
+          <t>B-</t>
+        </is>
+      </c>
+      <c r="AI2" s="1" t="inlineStr">
+        <is>
+          <t>C+</t>
+        </is>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>C-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -1019,6 +1085,36 @@
           <t>30 days from shipping</t>
         </is>
       </c>
+      <c r="AE3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
+      <c r="AF3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>30 calendar days</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -1169,6 +1265,36 @@
       <c r="AD4" s="2" t="inlineStr">
         <is>
           <t>No threshold, every device</t>
+        </is>
+      </c>
+      <c r="AE4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
+        </is>
+      </c>
+      <c r="AF4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
+        </is>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
+        </is>
+      </c>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>&gt; 5% Threshold</t>
         </is>
       </c>
     </row>
@@ -1255,6 +1381,12 @@
       <c r="AB5" s="4" t="n"/>
       <c r="AC5" s="4" t="n"/>
       <c r="AD5" s="4" t="n"/>
+      <c r="AE5" s="4" t="n"/>
+      <c r="AF5" s="4" t="n"/>
+      <c r="AG5" s="4" t="n"/>
+      <c r="AH5" s="4" t="n"/>
+      <c r="AI5" s="4" t="n"/>
+      <c r="AJ5" s="4" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -1291,6 +1423,12 @@
       <c r="AB6" s="7" t="n"/>
       <c r="AC6" s="7" t="n"/>
       <c r="AD6" s="7" t="n"/>
+      <c r="AE6" s="7" t="n"/>
+      <c r="AF6" s="7" t="n"/>
+      <c r="AG6" s="7" t="n"/>
+      <c r="AH6" s="7" t="n"/>
+      <c r="AI6" s="7" t="n"/>
+      <c r="AJ6" s="7" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
@@ -1439,6 +1577,36 @@
           <t>YES - Verizon Wireless carrier</t>
         </is>
       </c>
+      <c r="AE7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
+      <c r="AF7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
+      <c r="AG7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
+      <c r="AH7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
+      <c r="AI7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
+      <c r="AJ7" s="11" t="inlineStr">
+        <is>
+          <t>YES - TMO/Sprint/Metro carrier</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
@@ -1591,6 +1759,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AH8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AI8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ8" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
@@ -1743,6 +1941,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ9" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
@@ -1895,6 +2123,36 @@
           <t>YES</t>
         </is>
       </c>
+      <c r="AE10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ10" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
@@ -2045,6 +2303,36 @@
       <c r="AD11" s="10" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AE11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ11" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
         </is>
       </c>
     </row>
@@ -2083,6 +2371,12 @@
       <c r="AB12" s="7" t="n"/>
       <c r="AC12" s="7" t="n"/>
       <c r="AD12" s="7" t="n"/>
+      <c r="AE12" s="7" t="n"/>
+      <c r="AF12" s="7" t="n"/>
+      <c r="AG12" s="7" t="n"/>
+      <c r="AH12" s="7" t="n"/>
+      <c r="AI12" s="7" t="n"/>
+      <c r="AJ12" s="7" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
@@ -2235,6 +2529,36 @@
           <t>Not sure, need to test</t>
         </is>
       </c>
+      <c r="AE13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ13" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
@@ -2387,6 +2711,36 @@
           <t>Not sure, need to test</t>
         </is>
       </c>
+      <c r="AE14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ14" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
@@ -2539,6 +2893,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ15" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
@@ -2691,6 +3075,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ16" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
@@ -2843,6 +3257,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ17" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
@@ -2995,6 +3439,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ18" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
@@ -3143,6 +3617,36 @@
         </is>
       </c>
       <c r="AD19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AE19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AF19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AG19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AH19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AI19" s="10" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="AJ19" s="10" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -3183,6 +3687,12 @@
       <c r="AB20" s="7" t="n"/>
       <c r="AC20" s="7" t="n"/>
       <c r="AD20" s="7" t="n"/>
+      <c r="AE20" s="7" t="n"/>
+      <c r="AF20" s="7" t="n"/>
+      <c r="AG20" s="7" t="n"/>
+      <c r="AH20" s="7" t="n"/>
+      <c r="AI20" s="7" t="n"/>
+      <c r="AJ20" s="7" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
@@ -3335,6 +3845,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AF21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AG21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AH21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AI21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="AJ21" s="11" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
@@ -3487,6 +4027,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ22" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
@@ -3639,6 +4209,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ23" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
@@ -3791,6 +4391,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ24" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
@@ -3943,6 +4573,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ25" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
@@ -4095,6 +4755,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ26" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
@@ -4247,6 +4937,36 @@
           <t>NO</t>
         </is>
       </c>
+      <c r="AE27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ27" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
@@ -4397,6 +5117,36 @@
       <c r="AD28" s="10" t="inlineStr">
         <is>
           <t>NO</t>
+        </is>
+      </c>
+      <c r="AE28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AF28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AG28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AH28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AI28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
+        </is>
+      </c>
+      <c r="AJ28" s="9" t="inlineStr">
+        <is>
+          <t>Not sure, need to test</t>
         </is>
       </c>
     </row>
@@ -4435,6 +5185,12 @@
       <c r="AB29" s="12" t="n"/>
       <c r="AC29" s="12" t="n"/>
       <c r="AD29" s="12" t="n"/>
+      <c r="AE29" s="12" t="n"/>
+      <c r="AF29" s="12" t="n"/>
+      <c r="AG29" s="12" t="n"/>
+      <c r="AH29" s="12" t="n"/>
+      <c r="AI29" s="12" t="n"/>
+      <c r="AJ29" s="12" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -4471,6 +5227,12 @@
       <c r="AB30" s="12" t="n"/>
       <c r="AC30" s="12" t="n"/>
       <c r="AD30" s="12" t="n"/>
+      <c r="AE30" s="12" t="n"/>
+      <c r="AF30" s="12" t="n"/>
+      <c r="AG30" s="12" t="n"/>
+      <c r="AH30" s="12" t="n"/>
+      <c r="AI30" s="12" t="n"/>
+      <c r="AJ30" s="12" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
